--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484280_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484280_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8783</v>
+        <v>4.997</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8507</v>
+        <v>5.2146</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0276</v>
+        <v>-0.2176</v>
       </c>
       <c r="G2" t="n">
         <v>6.6613</v>
@@ -610,13 +610,13 @@
         <v>3.3208</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3537</v>
+        <v>0.4725</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0246</v>
+        <v>0.3392</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3784</v>
+        <v>0.1333</v>
       </c>
       <c r="V2" t="n">
         <v>-1.5507</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.299</v>
+        <v>1.9046</v>
       </c>
       <c r="E3" t="n">
-        <v>1.266</v>
+        <v>0.9765</v>
       </c>
       <c r="F3" t="n">
-        <v>1.033</v>
+        <v>0.9281</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5608</v>
+        <v>1.6818</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1962</v>
+        <v>0.8583</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3646</v>
+        <v>0.8235</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0635</v>
+        <v>2.6512</v>
       </c>
       <c r="K3" t="n">
-        <v>0.023</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0405</v>
+        <v>1.7686</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6243</v>
+        <v>-0.9694</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2192</v>
+        <v>-0.0243</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4051</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9534</v>
+        <v>2.7348</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8831</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1792</v>
+        <v>0.4741</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2961</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1762</v>
+        <v>1.6122</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7655</v>
+        <v>1.6704</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4107</v>
+        <v>-0.0582</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6818</v>
+        <v>-0.411</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8583</v>
+        <v>0.1553</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8235</v>
+        <v>-0.5663</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6512</v>
+        <v>-0.0062</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.0205</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7686</v>
+        <v>-0.0266</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9694</v>
+        <v>-0.4049</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0243</v>
+        <v>0.1348</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.5397</v>
       </c>
       <c r="P4" t="n">
-        <v>0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7348</v>
+        <v>0.1953</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1855</v>
+        <v>0.3673</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2631</v>
+        <v>0.216</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0775</v>
+        <v>0.1513</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4477</v>
+        <v>1.2298</v>
       </c>
       <c r="E5" t="n">
         <v>0.3647</v>
       </c>
       <c r="F5" t="n">
-        <v>1.083</v>
+        <v>0.8651</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4658</v>
@@ -844,13 +844,13 @@
         <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2689</v>
+        <v>1.051</v>
       </c>
       <c r="T5" t="n">
         <v>0.5944</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6745</v>
+        <v>0.4566</v>
       </c>
       <c r="V5" t="n">
         <v>0.2772</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3555</v>
+        <v>1.0178</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4681</v>
+        <v>0.012</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1127</v>
+        <v>1.0058</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.411</v>
+        <v>-0.5608</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1553</v>
+        <v>-0.1962</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5663</v>
+        <v>-0.3646</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0062</v>
+        <v>0.0635</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0205</v>
+        <v>0.023</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0266</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4049</v>
+        <v>-0.6243</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1348</v>
+        <v>-0.2192</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5397</v>
+        <v>-0.4051</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1106</v>
+        <v>0.6019</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0138</v>
+        <v>0.9253</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0968</v>
+        <v>-0.3234</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.5268</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.831</v>
+        <v>-0.1232</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8407</v>
+        <v>0.65</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6268</v>
@@ -1000,13 +1000,13 @@
         <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4644</v>
+        <v>0.9815</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2283</v>
+        <v>0.4795</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6927</v>
+        <v>0.502</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.334</v>
+        <v>0.45</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5753</v>
+        <v>1.1414</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9093</v>
+        <v>-0.6914</v>
       </c>
       <c r="G8" t="n">
         <v>0.3859</v>
@@ -1078,13 +1078,13 @@
         <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.892</v>
+        <v>-0.108</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5447</v>
+        <v>0.0214</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3473</v>
+        <v>-0.1294</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6093</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6034</v>
+        <v>-0.4302</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.644</v>
+        <v>-0.2802</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0407</v>
+        <v>-0.15</v>
       </c>
       <c r="G9" t="n">
         <v>0.1883</v>
@@ -1156,13 +1156,13 @@
         <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6196</v>
+        <v>-0.4464</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5915</v>
+        <v>-0.2276</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0282</v>
+        <v>-0.2188</v>
       </c>
       <c r="V9" t="n">
         <v>0.6093</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5915</v>
+        <v>-2.3942</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9775</v>
+        <v>0.2955</v>
       </c>
       <c r="F10" t="n">
-        <v>0.386</v>
+        <v>-2.6897</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2903</v>
+        <v>-1.3532</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6539</v>
+        <v>0.6429</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3636</v>
+        <v>-1.996</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1867</v>
+        <v>0.7452</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9555</v>
+        <v>0.7176</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7688</v>
+        <v>0.0276</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1036</v>
+        <v>-2.0984</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6984</v>
+        <v>-0.0747</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4052</v>
+        <v>-2.0237</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-1.1721</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.356</v>
+        <v>0.5916</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1732</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1828</v>
+        <v>-0.1308</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5545</v>
+        <v>-1.8279</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1097</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7326</v>
+        <v>-2.6504</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09320000000000001</v>
+        <v>-0.9316</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8258</v>
+        <v>-1.7188</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3532</v>
+        <v>-0.7671</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6429</v>
+        <v>-0.8885</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.996</v>
+        <v>0.1214</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7452</v>
+        <v>0.0716</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7176</v>
+        <v>0.0844</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0276</v>
+        <v>-0.0128</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0984</v>
+        <v>-0.8386</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0747</v>
+        <v>-0.9729</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0237</v>
+        <v>0.1342</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>2.3441</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2532</v>
+        <v>-1.2973</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5201</v>
+        <v>-0.5103</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2669</v>
+        <v>-0.787</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8279</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0281</v>
+        <v>-2.7816</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2549</v>
+        <v>-3.0587</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7733</v>
+        <v>0.2771</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7671</v>
+        <v>-1.2903</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8885</v>
+        <v>-1.6539</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1214</v>
+        <v>0.3636</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0716</v>
+        <v>-0.1867</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0844</v>
+        <v>-0.9555</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0128</v>
+        <v>0.7688</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8386</v>
+        <v>-1.1036</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9729</v>
+        <v>-0.6984</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1342</v>
+        <v>-0.4052</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3441</v>
+        <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.675</v>
+        <v>-0.5462</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8335</v>
+        <v>-0.2544</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8415</v>
+        <v>-0.2918</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
       <c r="W12" t="n">
-        <v>2.4373</v>
+        <v>-0.6642</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4373</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.876700000000002</v>
+        <v>3.481800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>4.676100000000001</v>
+        <v>5.2814</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7994</v>
+        <v>-1.799600000000001</v>
       </c>
       <c r="G13" t="n">
         <v>1.4423</v>
       </c>
       <c r="H13" t="n">
-        <v>7.512300000000001</v>
+        <v>7.5123</v>
       </c>
       <c r="I13" t="n">
         <v>-6.0699</v>
@@ -1447,7 +1447,7 @@
         <v>9.704700000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>4.726599999999999</v>
+        <v>4.7266</v>
       </c>
       <c r="M13" t="n">
         <v>-12.9887</v>
@@ -1468,13 +1468,13 @@
         <v>19.5341</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9768000000000001</v>
+        <v>1.5819</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1748</v>
+        <v>2.7799</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1979</v>
+        <v>-1.198</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4958</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.548400000000001</v>
+        <v>8.561400000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>7.4035</v>
+        <v>7.2012</v>
       </c>
       <c r="F14" t="n">
-        <v>1.145</v>
+        <v>1.3601</v>
       </c>
       <c r="G14" t="n">
         <v>3.9754</v>
@@ -1546,13 +1546,13 @@
         <v>3.1255</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5497</v>
+        <v>0.5627</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6027</v>
+        <v>0.4005</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.053</v>
+        <v>0.1622</v>
       </c>
       <c r="V14" t="n">
         <v>3.0466</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4795</v>
+        <v>1.6337</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5843</v>
+        <v>-0.4832</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0638</v>
+        <v>2.1169</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2358</v>
@@ -1624,13 +1624,13 @@
         <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1563</v>
+        <v>-0.0021</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0935</v>
+        <v>0.0076</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.0097</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2772</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8702</v>
+        <v>1.101</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6761</v>
+        <v>1.4739</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.806</v>
+        <v>-0.3729</v>
       </c>
       <c r="G16" t="n">
         <v>0.4407</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0154</v>
+        <v>0.2463</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7567</v>
+        <v>0.5545</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7413</v>
+        <v>-0.3083</v>
       </c>
       <c r="V16" t="n">
         <v>0.6093</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7175</v>
+        <v>0.928</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1739</v>
+        <v>2.3529</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4563</v>
+        <v>-1.4249</v>
       </c>
       <c r="G17" t="n">
-        <v>1.09</v>
+        <v>1.2526</v>
       </c>
       <c r="H17" t="n">
-        <v>0.065</v>
+        <v>-0.7851</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0251</v>
+        <v>2.0377</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2949</v>
+        <v>4.1287</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1.1461</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2949</v>
+        <v>2.9826</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2049</v>
+        <v>-2.8761</v>
       </c>
       <c r="N17" t="n">
-        <v>0.065</v>
+        <v>-1.9312</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2698</v>
+        <v>-0.9449</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3725</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.121</v>
+        <v>0.3729</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2515</v>
+        <v>-0.3069</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4806</v>
+        <v>0.7448</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5551</v>
+        <v>1.1739</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0745</v>
+        <v>-0.4291</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2526</v>
+        <v>1.09</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7851</v>
+        <v>0.065</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0377</v>
+        <v>1.0251</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1287</v>
+        <v>1.2949</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1461</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9826</v>
+        <v>1.2949</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.8761</v>
+        <v>-0.2049</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9312</v>
+        <v>0.065</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9449</v>
+        <v>-0.2698</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3813</v>
+        <v>-0.3453</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5752</v>
+        <v>-0.121</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9565</v>
+        <v>-0.2242</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3045</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2183</v>
+        <v>2.3194</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9138</v>
+        <v>-1.8049</v>
       </c>
       <c r="G19" t="n">
         <v>-0.405</v>
@@ -1936,13 +1936,13 @@
         <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2905</v>
+        <v>-0.0805</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3631</v>
+        <v>-0.262</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0726</v>
+        <v>0.1816</v>
       </c>
       <c r="V19" t="n">
         <v>0.6093</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2705</v>
+        <v>-0.0424</v>
       </c>
       <c r="E20" t="n">
-        <v>1.137</v>
+        <v>1.3392</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4075</v>
+        <v>-1.3816</v>
       </c>
       <c r="G20" t="n">
         <v>0.611</v>
@@ -2014,13 +2014,13 @@
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6862</v>
+        <v>-0.4581</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5447</v>
+        <v>-0.3425</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1415</v>
+        <v>-0.1156</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8238</v>
+        <v>-2.2416</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6489</v>
+        <v>-3.8633</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1749</v>
+        <v>1.6218</v>
       </c>
       <c r="G21" t="n">
-        <v>1.24</v>
+        <v>-3.0924</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2412</v>
+        <v>-0.9619</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4812</v>
+        <v>-2.1305</v>
       </c>
       <c r="J21" t="n">
-        <v>2.139</v>
+        <v>-1.2349</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6127</v>
+        <v>0.0857</v>
       </c>
       <c r="L21" t="n">
-        <v>2.7517</v>
+        <v>-1.3206</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.899</v>
+        <v>-1.8575</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-1.0476</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2704</v>
+        <v>-0.8099</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.5162</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.8603</v>
+        <v>-2.1488</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3441</v>
+        <v>2.7348</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1607</v>
+        <v>0.542</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0221</v>
+        <v>0.1845</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1828</v>
+        <v>0.3575</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3869</v>
+        <v>-0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>2.0503</v>
+        <v>-0.6642</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4373</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9388</v>
+        <v>-3.0001</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6723</v>
+        <v>-1.8511</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7334</v>
+        <v>-1.1491</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0924</v>
+        <v>1.24</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9619</v>
+        <v>-1.2412</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1305</v>
+        <v>2.4812</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2349</v>
+        <v>2.139</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0857</v>
+        <v>-0.6127</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3206</v>
+        <v>2.7517</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8575</v>
+        <v>-0.899</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0476</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8099</v>
+        <v>-0.2704</v>
       </c>
       <c r="P22" t="n">
-        <v>0.586</v>
+        <v>-3.5162</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1488</v>
+        <v>-5.8603</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7348</v>
+        <v>2.3441</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1553</v>
+        <v>-0.337</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6244</v>
+        <v>-0.1801</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4692</v>
+        <v>-0.1569</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2772</v>
+        <v>-0.3869</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>2.0503</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3869</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8879</v>
+        <v>-3.8464</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8207</v>
+        <v>-1.0229</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0673</v>
+        <v>-2.8235</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1367</v>
@@ -2248,13 +2248,13 @@
         <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1419</v>
+        <v>-0.1004</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3247</v>
+        <v>0.1225</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4667</v>
+        <v>-0.2229</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3562</v>
+        <v>-5.2071</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.6381</v>
+        <v>-6.8404</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2819</v>
+        <v>1.6333</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1824</v>
@@ -2326,13 +2326,13 @@
         <v>2.9301</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.952</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6633</v>
+        <v>0.461</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1396</v>
+        <v>0.491</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8279</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.876500000000001</v>
+        <v>-0.854099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>1.799600000000002</v>
+        <v>1.799599999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.676199999999999</v>
+        <v>-2.6539</v>
       </c>
       <c r="G25" t="n">
         <v>-1.4426</v>
@@ -2404,22 +2404,22 @@
         <v>17.5809</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9766999999999999</v>
+        <v>1.0457</v>
       </c>
       <c r="T25" t="n">
-        <v>1.198</v>
+        <v>1.1979</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.1747</v>
+        <v>-0.1522</v>
       </c>
       <c r="V25" t="n">
         <v>1.496</v>
       </c>
       <c r="W25" t="n">
-        <v>7.147099999999999</v>
+        <v>7.1471</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.651300000000001</v>
+        <v>-5.6513</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484280_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484280_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,47 +549,52 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.997</v>
+        <v>3.4761</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2146</v>
+        <v>3.6936</v>
       </c>
       <c r="F2" t="n">
         <v>-0.2176</v>
       </c>
       <c r="G2" t="n">
-        <v>6.6613</v>
+        <v>5.1403</v>
       </c>
       <c r="H2" t="n">
-        <v>7.458</v>
+        <v>7.151</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7967</v>
+        <v>-2.0107</v>
       </c>
       <c r="J2" t="n">
-        <v>9.1143</v>
+        <v>7.5933</v>
       </c>
       <c r="K2" t="n">
-        <v>7.6171</v>
+        <v>7.3101</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4972</v>
+        <v>0.2833</v>
       </c>
       <c r="M2" t="n">
         <v>-2.453</v>
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -714,7 +729,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -782,231 +797,246 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2298</v>
+        <v>1.521</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3647</v>
+        <v>1.521</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8651</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4658</v>
+        <v>1.521</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.845</v>
+        <v>0.307</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6208</v>
+        <v>1.214</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3116</v>
+        <v>1.521</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.0399</v>
+        <v>0.307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7284</v>
+        <v>1.214</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1542</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1949</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3492</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.051</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5944</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4566</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0178</v>
+        <v>1.2298</v>
       </c>
       <c r="E6" t="n">
-        <v>0.012</v>
+        <v>0.3647</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0058</v>
+        <v>0.8651</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5608</v>
+        <v>-1.4658</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1962</v>
+        <v>-0.845</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3646</v>
+        <v>-0.6208</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0635</v>
+        <v>-0.3116</v>
       </c>
       <c r="K6" t="n">
-        <v>0.023</v>
+        <v>-1.0399</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>0.7284</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6243</v>
+        <v>-1.1542</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2192</v>
+        <v>0.1949</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4051</v>
+        <v>-1.3492</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6019</v>
+        <v>1.051</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9253</v>
+        <v>0.5944</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3234</v>
+        <v>0.4566</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>A. RECIO PINOL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5268</v>
+        <v>0.7108</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1232</v>
+        <v>-0.295</v>
       </c>
       <c r="F7" t="n">
-        <v>0.65</v>
+        <v>1.0058</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6268</v>
+        <v>-0.8678</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8527</v>
+        <v>-0.5032</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.4795</v>
+        <v>-0.3646</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4074</v>
+        <v>-0.2435</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4531</v>
+        <v>-0.284</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8604</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2194</v>
+        <v>-0.6243</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3996</v>
+        <v>-0.2192</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.619</v>
+        <v>-0.4051</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9815</v>
+        <v>0.6019</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4795</v>
+        <v>0.9253</v>
       </c>
       <c r="U7" t="n">
-        <v>0.502</v>
+        <v>-0.3234</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1016,714 +1046,760 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.45</v>
+        <v>0.5268</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1414</v>
+        <v>-0.1232</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6914</v>
+        <v>0.65</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3859</v>
+        <v>-1.6268</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1287</v>
+        <v>1.8527</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2572</v>
+        <v>-3.4795</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2102</v>
+        <v>-0.4074</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1433</v>
+        <v>1.4531</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0669</v>
+        <v>-1.8604</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8243</v>
+        <v>-1.2194</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0146</v>
+        <v>0.3996</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8097</v>
+        <v>-1.619</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.108</v>
+        <v>0.9815</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0214</v>
+        <v>0.4795</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1294</v>
+        <v>0.502</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4302</v>
+        <v>0.45</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2802</v>
+        <v>1.1414</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.15</v>
+        <v>-0.6914</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1883</v>
+        <v>0.3859</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0.1287</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1883</v>
+        <v>0.2572</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4869</v>
+        <v>1.2102</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7585</v>
+        <v>0.1433</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7284</v>
+        <v>1.0669</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2986</v>
+        <v>-0.8243</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7585</v>
+        <v>-0.0146</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5401</v>
+        <v>-0.8097</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4464</v>
+        <v>-0.108</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2276</v>
+        <v>0.0214</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2188</v>
+        <v>-0.1294</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6093</v>
+        <v>-0.6093</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6093</v>
+        <v>0.8865</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3942</v>
+        <v>0.307</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2955</v>
+        <v>0.307</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6897</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3532</v>
+        <v>0.307</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6429</v>
+        <v>0.307</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.996</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7452</v>
+        <v>0.307</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7176</v>
+        <v>0.307</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0276</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0984</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0747</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0237</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5916</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7223000000000001</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1308</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6504</v>
+        <v>0.307</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9316</v>
+        <v>0.307</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7188</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7671</v>
+        <v>0.307</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8885</v>
+        <v>0.307</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1214</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0716</v>
+        <v>0.307</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0844</v>
+        <v>0.307</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0128</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8386</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9729</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1342</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2973</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5103</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.787</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7816</v>
+        <v>-0.4302</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0587</v>
+        <v>-0.2802</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2771</v>
+        <v>-0.15</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2903</v>
+        <v>0.1883</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6539</v>
+        <v>-0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3636</v>
+        <v>0.1883</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1867</v>
+        <v>1.4869</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9555</v>
+        <v>0.7585</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7688</v>
+        <v>0.7284</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1036</v>
+        <v>-1.2986</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6984</v>
+        <v>-0.7585</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4052</v>
+        <v>-0.5401</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3907</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5462</v>
+        <v>-0.4464</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2544</v>
+        <v>-0.2276</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2918</v>
+        <v>-0.2188</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5545</v>
+        <v>0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6642</v>
+        <v>0.6093</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1097</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.481800000000001</v>
+        <v>-2.3942</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2814</v>
+        <v>0.2955</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.799600000000001</v>
+        <v>-2.6897</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4423</v>
+        <v>-1.3532</v>
       </c>
       <c r="H13" t="n">
-        <v>7.5123</v>
+        <v>0.6429</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.0699</v>
+        <v>-1.996</v>
       </c>
       <c r="J13" t="n">
-        <v>14.431</v>
+        <v>0.7452</v>
       </c>
       <c r="K13" t="n">
-        <v>9.704700000000001</v>
+        <v>0.7176</v>
       </c>
       <c r="L13" t="n">
-        <v>4.7266</v>
+        <v>0.0276</v>
       </c>
       <c r="M13" t="n">
-        <v>-12.9887</v>
+        <v>-2.0984</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.1924</v>
+        <v>-0.0747</v>
       </c>
       <c r="O13" t="n">
-        <v>-10.7965</v>
+        <v>-2.0237</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.5808</v>
+        <v>-1.1721</v>
       </c>
       <c r="R13" t="n">
-        <v>19.5341</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5819</v>
+        <v>0.5916</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7799</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.198</v>
+        <v>-0.1308</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4958</v>
+        <v>-1.8279</v>
       </c>
       <c r="W13" t="n">
-        <v>5.6513</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.1472</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB. CORNELLÀ</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.561400000000001</v>
+        <v>-2.7816</v>
       </c>
       <c r="E14" t="n">
-        <v>7.2012</v>
+        <v>-3.0587</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3601</v>
+        <v>0.2771</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9754</v>
+        <v>-1.2903</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3315</v>
+        <v>-1.6539</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6439</v>
+        <v>0.3636</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6843</v>
+        <v>-0.1867</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1744</v>
+        <v>-0.9555</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5099</v>
+        <v>0.7688</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7089</v>
+        <v>-1.1036</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8429</v>
+        <v>-0.6984</v>
       </c>
       <c r="O14" t="n">
-        <v>0.134</v>
+        <v>-0.4052</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1255</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5627</v>
+        <v>-0.5462</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4005</v>
+        <v>-0.2544</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1622</v>
+        <v>-0.2918</v>
       </c>
       <c r="V14" t="n">
-        <v>3.0466</v>
+        <v>-0.5545</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2652</v>
+        <v>-0.6642</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2186</v>
+        <v>0.1097</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB. CORNELLÀ</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6337</v>
+        <v>-2.9574</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4832</v>
+        <v>-1.2386</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1169</v>
+        <v>-1.7188</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2358</v>
+        <v>-1.0741</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1256</v>
+        <v>-1.1955</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8899</v>
+        <v>0.1214</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4908</v>
+        <v>-0.2354</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5718</v>
+        <v>-0.2226</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0809</v>
+        <v>-0.0128</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2551</v>
+        <v>-0.8386</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5538</v>
+        <v>-0.9729</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8089</v>
+        <v>0.1342</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1488</v>
+        <v>-0.586</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0021</v>
+        <v>-1.2973</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0076</v>
+        <v>-0.5103</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0097</v>
+        <v>-0.787</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CB. CORNELLÀ</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.101</v>
+        <v>3.481900000000002</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4739</v>
+        <v>5.2814</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3729</v>
+        <v>-1.7996</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4407</v>
+        <v>1.4423</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5357</v>
+        <v>7.512300000000002</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0949</v>
+        <v>-6.0699</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8142</v>
+        <v>14.431</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9644</v>
+        <v>9.704699999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8498</v>
+        <v>4.7267</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3735</v>
+        <v>-12.9887</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4287</v>
+        <v>-2.1924</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9447</v>
+        <v>-10.7965</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1721</v>
+        <v>-17.5808</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>19.5341</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2463</v>
+        <v>1.5819</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5545</v>
+        <v>2.7799</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3083</v>
+        <v>-1.198</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6093</v>
+        <v>-1.4958</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>5.651299999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3321</v>
-      </c>
+        <v>-7.1472</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.928</v>
+        <v>8.561400000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3529</v>
+        <v>7.2012</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4249</v>
+        <v>1.3601</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2526</v>
+        <v>3.9754</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7851</v>
+        <v>1.3315</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0377</v>
+        <v>2.6439</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1287</v>
+        <v>4.6843</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1461</v>
+        <v>2.1744</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9826</v>
+        <v>2.5099</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8761</v>
+        <v>-0.7089</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9312</v>
+        <v>-0.8429</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9449</v>
+        <v>0.134</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.1488</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>3.1255</v>
       </c>
       <c r="S17" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.5627</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3729</v>
+        <v>0.4005</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3069</v>
+        <v>0.1622</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3.0466</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4.2652</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7448</v>
+        <v>1.6337</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1739</v>
+        <v>-0.4832</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4291</v>
+        <v>2.1169</v>
       </c>
       <c r="G18" t="n">
-        <v>1.09</v>
+        <v>-0.2358</v>
       </c>
       <c r="H18" t="n">
-        <v>0.065</v>
+        <v>-1.1256</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0251</v>
+        <v>0.8899</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2949</v>
+        <v>-0.4908</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.5718</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2949</v>
+        <v>0.0809</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2049</v>
+        <v>0.2551</v>
       </c>
       <c r="N18" t="n">
-        <v>0.065</v>
+        <v>-0.5538</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2698</v>
+        <v>0.8089</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1488</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.1488</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3453</v>
+        <v>-0.0021</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.121</v>
+        <v>0.0076</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2242</v>
+        <v>-0.0097</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MASLLORENS MANRIQUE</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5145999999999999</v>
+        <v>1.101</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3194</v>
+        <v>1.4739</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8049</v>
+        <v>-0.3729</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.405</v>
+        <v>0.4407</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3239</v>
+        <v>0.5357</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.0949</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3628</v>
+        <v>1.8142</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6344</v>
+        <v>0.9644</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7284</v>
+        <v>0.8498</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7678</v>
+        <v>-1.3735</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9583</v>
+        <v>-0.4287</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8095</v>
+        <v>-0.9447</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0805</v>
+        <v>0.2463</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.262</v>
+        <v>0.5545</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1816</v>
+        <v>-0.3083</v>
       </c>
       <c r="V19" t="n">
         <v>0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6093</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +2060,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0424</v>
+        <v>0.928</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3392</v>
+        <v>2.3529</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3816</v>
+        <v>-1.4249</v>
       </c>
       <c r="G20" t="n">
-        <v>0.611</v>
+        <v>1.2526</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4664</v>
+        <v>-0.7851</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0774</v>
+        <v>2.0377</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6584</v>
+        <v>4.1287</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0409</v>
+        <v>1.1461</v>
       </c>
       <c r="L20" t="n">
-        <v>2.6174</v>
+        <v>2.9826</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0474</v>
+        <v>-2.8761</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5073</v>
+        <v>-1.9312</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5401</v>
+        <v>-0.9449</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4581</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3425</v>
+        <v>0.3729</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1156</v>
+        <v>-0.3069</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2030,6 +2121,11 @@
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2416</v>
+        <v>0.921</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8633</v>
+        <v>0.921</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6218</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0924</v>
+        <v>0.921</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9619</v>
+        <v>0.921</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1305</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2349</v>
+        <v>0.921</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0857</v>
+        <v>0.921</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3206</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8575</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0476</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8099</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7348</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.542</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1845</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3575</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0001</v>
+        <v>0.7448</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8511</v>
+        <v>1.1739</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1491</v>
+        <v>-0.4291</v>
       </c>
       <c r="G22" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2412</v>
+        <v>0.065</v>
       </c>
       <c r="I22" t="n">
-        <v>2.4812</v>
+        <v>1.0251</v>
       </c>
       <c r="J22" t="n">
-        <v>2.139</v>
+        <v>1.2949</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6127</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2.7517</v>
+        <v>1.2949</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.899</v>
+        <v>-0.2049</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2704</v>
+        <v>-0.2698</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.5162</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.8603</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.337</v>
+        <v>-0.3453</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1801</v>
+        <v>-0.121</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1569</v>
+        <v>-0.2242</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.0503</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>A. MASLLORENS MANRIQUE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2309,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8464</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0229</v>
+        <v>2.3194</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8235</v>
+        <v>-1.8049</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.1367</v>
+        <v>-0.405</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8146</v>
+        <v>-0.3239</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3221</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1454</v>
+        <v>1.3628</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3073</v>
+        <v>0.6344</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1619</v>
+        <v>0.7284</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9913</v>
+        <v>-1.7678</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5073</v>
+        <v>-0.9583</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.484</v>
+        <v>-0.8095</v>
       </c>
       <c r="P23" t="n">
         <v>0.3907</v>
@@ -2248,28 +2354,33 @@
         <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1004</v>
+        <v>-0.0805</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1225</v>
+        <v>-0.262</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2229</v>
+        <v>0.1816</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. MAYO SCHWANDT</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2071</v>
+        <v>-0.0424</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.8404</v>
+        <v>1.3392</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6333</v>
+        <v>-1.3816</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1824</v>
+        <v>0.611</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7258</v>
+        <v>-1.4664</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4566</v>
+        <v>2.0774</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2225</v>
+        <v>2.6584</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.362</v>
+        <v>0.0409</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.8604</v>
+        <v>2.6174</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0401</v>
+        <v>-2.0474</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3638</v>
+        <v>-1.5073</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4039</v>
+        <v>-0.5401</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.0789</v>
+        <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>2.9301</v>
+        <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>0.952</v>
+        <v>-0.4581</v>
       </c>
       <c r="T24" t="n">
-        <v>0.461</v>
+        <v>-0.3425</v>
       </c>
       <c r="U24" t="n">
-        <v>0.491</v>
+        <v>-0.1156</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,401 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.854099999999999</v>
+        <v>-3.0001</v>
       </c>
       <c r="E25" t="n">
-        <v>1.799599999999999</v>
+        <v>-1.8511</v>
       </c>
       <c r="F25" t="n">
+        <v>-1.1491</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.2412</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.4812</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.139</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.6127</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2.7517</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.899</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.6284999999999999</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.2704</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-3.5162</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-5.8603</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.3441</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.337</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.1801</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.1569</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.3869</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.0503</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R. PEREZ GALINDO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-3.1625</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-4.7843</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.6218</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-4.0133</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.8828</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.1305</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.1559</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.8353</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.3206</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.8575</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.0476</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.8099</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.7348</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P. MARTINEZ FERIA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-3.8464</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-1.0229</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-2.8235</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-4.1367</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-2.8146</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.3221</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.1454</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.3073</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-2.9913</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1.5073</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-1.484</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.1004</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.2229</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>I. MAYO SCHWANDT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-5.2071</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-6.8404</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.6333</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-2.1824</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.7258</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-1.4566</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-2.2225</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.362</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-1.8604</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.3638</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-5.0789</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.9301</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484280_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.8539999999999992</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.799600000000001</v>
+      </c>
+      <c r="F29" t="n">
         <v>-2.6539</v>
       </c>
-      <c r="G25" t="n">
-        <v>-1.4426</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-7.5123</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="G29" t="n">
+        <v>-1.442499999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-7.5122</v>
+      </c>
+      <c r="I29" t="n">
         <v>6.069999999999999</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J29" t="n">
         <v>12.9887</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K29" t="n">
         <v>2.1921</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L29" t="n">
         <v>10.7965</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M29" t="n">
         <v>-14.4312</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N29" t="n">
         <v>-9.7044</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O29" t="n">
         <v>-4.7265</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P29" t="n">
         <v>-1.9534</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q29" t="n">
         <v>-19.5344</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R29" t="n">
         <v>17.5809</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S29" t="n">
         <v>1.0457</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T29" t="n">
         <v>1.1979</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U29" t="n">
         <v>-0.1522</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V29" t="n">
         <v>1.496</v>
       </c>
-      <c r="W25" t="n">
-        <v>7.1471</v>
-      </c>
-      <c r="X25" t="n">
-        <v>-5.6513</v>
-      </c>
+      <c r="W29" t="n">
+        <v>7.147099999999999</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-5.651300000000001</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
